--- a/testdata/partner_products.xlsx
+++ b/testdata/partner_products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\onsumaye\Desktop\html\intel_edge_ai_automation\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33454EA6-07A8-4ABA-965A-5D7EE03761DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CEC4683-C4BC-4909-8561-E1061DCAF8CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
   <si>
     <t>enabled</t>
   </si>
@@ -34,9 +34,6 @@
     <t>product_name</t>
   </si>
   <si>
-    <t>application_name</t>
-  </si>
-  <si>
     <t>product_type</t>
   </si>
   <si>
@@ -52,15 +49,9 @@
     <t>expected_description</t>
   </si>
   <si>
-    <t>expected_breadcrumb</t>
-  </si>
-  <si>
     <t>expected_meta_description</t>
   </si>
   <si>
-    <t>expected_og_title</t>
-  </si>
-  <si>
     <t>expected_keywords</t>
   </si>
   <si>
@@ -79,142 +70,82 @@
     <t>expected_pdf_text</t>
   </si>
   <si>
+    <t>expected_resource_url</t>
+  </si>
+  <si>
+    <t>partner_dropdown_label</t>
+  </si>
+  <si>
     <t>category_subcategory</t>
   </si>
   <si>
-    <t>expected_resource_url</t>
-  </si>
-  <si>
-    <t>partner_dropdown_label</t>
-  </si>
-  <si>
     <t>PS-001</t>
   </si>
   <si>
-    <t>Advantech</t>
-  </si>
-  <si>
-    <t>Advantech UNO-258</t>
-  </si>
-  <si>
-    <t>System</t>
-  </si>
-  <si>
-    <t>Fanless Edge AI Box PC for Smart Manufacturing</t>
-  </si>
-  <si>
-    <t>The UNO-258 is Advantech's next-generation fanless Edge AI Box PC designed to accelerate real-time AI applications in smart manufacturing, machine vision, and industrial automation. Powered by Intel® Core™ Ultra Series 3 processors, the system delivers up to 180 TOPS AI performance through integrated CPU, GPU, and NPU architecture, enabling low-latency AI inference directly at the edge. As industrial environments increasingly demand real-time inspection, autonomous operation, and AI-driven analytics, traditional systems often struggle with thermal limitations, unstable operation, and complex deployment. UNO-258 addresses these challenges with a rugged fanless design, wide-temperature operation, and industrial-grade reliability for harsh environments. The compact platform supports high-speed connectivity, multiple vision and industrial I/O interfaces, and flexible expansion capabilities, making it ideal for Vision AI, robotics, smart transportation, and edge automation applications. Compared with conventional industrial PCs, UNO-258 combines high AI computing performance, fanless durability, and simplified deployment into a compact edge-ready platform optimized for next-generation Edge AI workloads.</t>
-  </si>
-  <si>
-    <t>Engagement &gt; Solution Hub &gt; Edge AI Catalog &gt; Edge AI Partner Spotlight &gt; Advantech UNO-258</t>
-  </si>
-  <si>
-    <t>The UNO-258 is Advantech's next-generation fanless Edge AI Box PC designed to accelerate real-time AI applications in smart manufacturing, machine</t>
-  </si>
-  <si>
-    <t>1. High-performance Computing
-2. Integrated AI Acceleration
-3. Compact Fanless Design
-4. Rich I/O &amp; Fast Connectivity</t>
-  </si>
-  <si>
-    <t>Edge Feature: Extended Temperature, Real-time
-Vertical: Manufacturing; Robotics
-Open Software Platform: Robotics AI Suite, Manufacturing AI Suite
-Intel Processors: Intel Core Ultra Series 3 processors
-Geo Availability: Worldwide; US/Canada; Latin America Region; Europe, Middle East, and Africa; Asia Pacific, Japan, Australia &amp; New Zealand; PRC; India
-AI Edge System Sizing: TBC
-Target Audience: SI (System Integrators)</t>
-  </si>
-  <si>
-    <t>https://www.advantech.com/en/contact</t>
-  </si>
-  <si>
-    <t>https://www.advantech.com/en/products/9a0cc561-8fc2-4e22-969c-9df90a3952b5/uno-258/mod_d527f9c1-6844-48ed-a512-e10c146dbea0</t>
-  </si>
-  <si>
-    <t>Advantech Co. Ltd.</t>
+    <t>Ecrio</t>
+  </si>
+  <si>
+    <t>Ecrio Edge AI Communication Platform</t>
+  </si>
+  <si>
+    <t>application</t>
+  </si>
+  <si>
+    <t>Low Latency Edge AI for PPE Detection &amp; Multi-Modal Alerting</t>
+  </si>
+  <si>
+    <t>Ecrio’s Edge AI Communication Platform enables AI-powered worker safety and mission-critical communications for Human-Oversight of automation by combining real-time video analytics and voice processing at the edge. The solution supports use cases such as Personal Protective Equipment (PPE) detection and voice-driven workflows by processing vision and voice data locally, close to where it is generated. Running on containerized workloads, the solution is optimized with OpenVINO™ toolkit, accelerating vision and speech inference on AI PCs powered by Intel® Core™ Ultra 200V series processors. The edge-focused architecture delivers low-latency, real-time decision-making while reducing reliance on centralized cloud infrastructure. Designed for safety-critical operations, the platform delivers resilient, always-on performance even in bandwidth-limited or disconnected environments. Local AI processing enhances data privacy, supports regulatory compliance, and enables consistent, scalable deployment across distributed worksites.</t>
+  </si>
+  <si>
+    <t>1. Real-Time Edge AI
+2. On-Device Vision
+3. Low-Latency Voice
+4. Cost-Efficient</t>
+  </si>
+  <si>
+    <t>Vertical: Video Safety &amp; Critical Infrastructure, Manufacturing
+Use Cases: Worker Safety​; Operational Diagnostics; Operational Efficiency
+Open Software Platform: OpenVINO Tool Kit
+Intel Technologies: Intel® Core™ Ultra processors (Series 2)
+Geo Availability: Worldwide</t>
+  </si>
+  <si>
+    <t>https://www.ecrio.com/contact/</t>
+  </si>
+  <si>
+    <t>https://www.ecrio.com/</t>
   </si>
   <si>
     <t>PS-002</t>
   </si>
   <si>
-    <t>ASUS</t>
-  </si>
-  <si>
-    <t>ASUS NUC 15 Pro+</t>
-  </si>
-  <si>
-    <t>system</t>
-  </si>
-  <si>
-    <t>NUC</t>
-  </si>
-  <si>
-    <t>NUC 15 Pro</t>
-  </si>
-  <si>
-    <t>Engagement &gt; Solution Hub &gt; Edge AI Catalog &gt; Edge AI Partner Spotlight &gt; ASUS NUC 15 Pro+</t>
-  </si>
-  <si>
-    <t>asus</t>
-  </si>
-  <si>
-    <t>PS-003</t>
-  </si>
-  <si>
-    <t>Vecow</t>
-  </si>
-  <si>
-    <t>Vecow ECX-3200</t>
-  </si>
-  <si>
-    <t>ECX</t>
-  </si>
-  <si>
-    <t>ECX-3200</t>
-  </si>
-  <si>
-    <t>Engagement &gt; Solution Hub &gt; Edge AI Catalog &gt; Edge AI Partner Spotlight &gt; Vecow ECX-3200</t>
-  </si>
-  <si>
-    <t>vecow</t>
-  </si>
-  <si>
-    <t>PS-004</t>
-  </si>
-  <si>
-    <t>Brysk Inc.</t>
-  </si>
-  <si>
-    <t>Smart IoT Vending Fridge</t>
-  </si>
-  <si>
-    <t>Application</t>
-  </si>
-  <si>
-    <t>Frictionless Grab-and-Go Smart Retail</t>
-  </si>
-  <si>
-    <t>Brysk Smart IoT Vending Fridge redefines unattended retail with a frictionless, grab-and-go experience powered by camera-only computer vision at the edge. Shoppers simply open the fridge, pick items, and walk away — no pre-selection, no queues, and no mechanical vending constraints. Built on Intel® Core™ and Intel® Core™ Ultra processors, the solution uses the OpenVINO™ toolkit, Deep Learning Streamer, and Intel® AI-Optimized Vision Processing to accurately detect pick-up and return events in real time. By eliminating weight sensors, RFID, and complex mechanics, Brysk reduces hardware complexity, maintenance costs, and deployment time while improving checkout speed and order accuracy. Brysk Smart IoT Vending Fridge delivers reliable, scalable computer vision performance for modern retail environments seeking higher convenience, lower pilferage, and always-on autonomous operation.</t>
-  </si>
-  <si>
-    <t>Engagement &gt; Solution Hub &gt; Edge AI Catalog &gt; Edge AI Partner Spotlight &gt; Smart IoT Vending Fridge</t>
+    <t>Dynamo AI</t>
+  </si>
+  <si>
+    <t>DynamoGuard On-Device</t>
+  </si>
+  <si>
+    <t>Secure, Real-time Al Guardrails at the Device Level</t>
+  </si>
+  <si>
+    <t>DynamoGuard On-Device, powered by Intel® Core™ Ultra processors, delivers real-time on-device guardrails that help enterprises adopt generative Al securely and responsibly. Many organizations lack the oversight, compliance, and data protection needed for safe Al adoption. This solution enables IT teams to rapidly create, customize, and enforce policies that filter Al interactions before transmission—ensuring sensitive inputs never leave the device. With ultra-low latency (&lt;40ms GPU, &lt;135ms NPU) and lightweight guardrail models optimized using the OpenVINO™ toolkit, DynamoGuard minimizes performance overhead while maximizing security. Enterprises gain a single observability platform for monitoring Al usage, real-time compliance enforcement, and hallucination checks. The result is a powerful combination of speed, control, and protection, enabling confident, large-scale deployment of GenAI across enterprise fleets.</t>
+  </si>
+  <si>
+    <t>.Real-Time Guardrails
+.On-Device Compliance
+.Ultra-Low Latency</t>
   </si>
   <si>
     <t>Device Type: Edge Device
-Vertical: Retail</t>
-  </si>
-  <si>
-    <t>https://www.brysk.com/ai_vending</t>
-  </si>
-  <si>
-    <t>Device Type: Edge Device
-Vertical: Retail
-Use Cases: Self-Checkout​; Loss Prevention​; Order Accuracy; Product Recognition (detection, classification, tracking)​; Full Pipeline (product, weight, text, barcode)​; Age Verification​; Items in Basket​; Shopper Behavior​; Order Validation​
-Open Software Platform: OpenVINO Tool Kit, Intel Deep Learning Streamer
-Intel Technologies: 13th Gen Intel® Core™ processors; 14th Gen Intel® Core™ processors; Intel® Core™ processors (Series 1); Intel® Core™ processors (Series 2); Intel® Core™ Ultra processors (Series 1); Intel® Core™ Ultra processors (Series 2);
-Geo Availability: Worldwide; US/Canada; Europe, Middle East, and Africa; India</t>
+Open Software Platform: OpenVINO Tool Kit
+Intel Technologies: Intel® Core™ Ultra processors (Series 1)
+Geo Availability: Worldwide</t>
+  </si>
+  <si>
+    <t>mailto:patrick@dynamofl.com</t>
+  </si>
+  <si>
+    <t>https://www.dynamo.ai/</t>
   </si>
 </sst>
 </file>
@@ -250,11 +181,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -557,10 +485,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -618,226 +546,111 @@
       <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" t="s">
-        <v>21</v>
-      </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="b">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
         <v>22</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" t="s">
         <v>23</v>
       </c>
-      <c r="D2" t="s">
+      <c r="I2" t="s">
         <v>24</v>
       </c>
-      <c r="E2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="J2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s">
         <v>25</v>
       </c>
-      <c r="G2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="M2" t="s">
         <v>26</v>
       </c>
-      <c r="J2" t="s">
+      <c r="N2" t="s">
         <v>27</v>
       </c>
-      <c r="K2" t="s">
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="s">
         <v>28</v>
       </c>
-      <c r="L2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2" t="s">
-        <v>30</v>
-      </c>
-      <c r="P2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>32</v>
-      </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T2" t="s">
-        <v>31</v>
-      </c>
-      <c r="U2" t="s">
-        <v>33</v>
-      </c>
-      <c r="V2" t="s">
-        <v>34</v>
+      <c r="R2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S2" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="b">
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3" t="s">
         <v>35</v>
       </c>
-      <c r="C3" t="s">
+      <c r="N3" t="s">
         <v>36</v>
       </c>
-      <c r="D3" t="s">
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="s">
         <v>37</v>
       </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>42</v>
-      </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" t="b">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I4" t="s">
-        <v>46</v>
-      </c>
-      <c r="J4" t="s">
-        <v>47</v>
-      </c>
-      <c r="K4" t="s">
-        <v>48</v>
-      </c>
-      <c r="L4" t="s">
-        <v>46</v>
-      </c>
-      <c r="M4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>49</v>
-      </c>
-      <c r="R4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A5" t="b">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G5" t="s">
-        <v>52</v>
-      </c>
-      <c r="H5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I5" t="s">
-        <v>54</v>
-      </c>
-      <c r="J5" t="s">
-        <v>55</v>
-      </c>
-      <c r="K5" t="s">
-        <v>56</v>
-      </c>
-      <c r="L5" t="s">
-        <v>52</v>
-      </c>
-      <c r="M5" t="s">
-        <v>52</v>
-      </c>
-      <c r="P5" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>58</v>
-      </c>
-      <c r="R5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="V5" t="s">
-        <v>51</v>
+      <c r="R3" t="s">
+        <v>30</v>
+      </c>
+      <c r="S3" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/partner_products.xlsx
+++ b/testdata/partner_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,21 +528,21 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25102</v>
+        <v>25185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Arcee</t>
+          <t>AIREV</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Arcee</t>
+          <t>AIREV</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arcee Foundation Models (AFM)</t>
+          <t>AIREV OnDemand</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -552,59 +552,57 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Arcee Foundation Models (AFM)</t>
+          <t>AIREV OnDemand</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Arcee Foundation Models (AFM)</t>
+          <t>AIREV OnDemand</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Enterprise-Ready AI Models Built for Accuracy</t>
+          <t>Sovereign Agentic AI OS for Enterprise Automation</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>AFM delivers enterprise-scale AI power without enterprise-scale infrastructure. Built for modest hardware and seamless deployment, AFM enables faster, more affordable launch and scaling of powerful language model solutions, at a fraction of the hosting cost of much larger LLMs while matching performance. Optimized for low-RAM GPUs or even CPUs, AFM is ideal for constrained environments, edge devices, or cost-sensitive use cases. Unlike black-box models, AFM is fully open: open architecture, open weights, and no vendor lock-in. You can deploy AFM in any
-environment, on-premises, in the cloud, or hybrid, and integrate it using popular open-source frameworks like Hugging Face Transformers, vLLM, or llama.cpp. AFM also includes native support for function calling and agentic reasoning, enabling tool use and workflow automation without fragile prompt chains. Trained on clean, legally sound data, AFM-4.SB performs across 1O+ languages.</t>
+          <t>AIREV's OnDemand is an all-in-one no/low-code agentic AI platform and decentralized
+operating system that enables businesses to create, deploy, and manage autonomous AI agents, RAG applications, and intelligent automation workflows across cloud, on-premises, and hybrid environments. It transforms operations by automating workflows end-to-end with intelligence that learns, collaborates, and evolves in real time—delivering value in weeks, not months. OnDemand features a secure marketplace of 1,200+ specialized agents, visual workflow orchestration, BYOM/BYOI support, batch processing, multilingual capabilities, team collaboration, and enterprise-grade controls. Powered by Intel®, Intel® Xeon® 6 processors optimize low-latency inference for smaller models (≤10B parameters), while Intel® Gaudi® 3 accelerators enable high-concurrency LLM inference—creating a unified AI stack for faster automation, lower TCO, and enterprise-grade scalability and security.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1. Edge Inferencing
-2. Cost-Effective
-3. Open Architecture
-4. Tool Compatibility</t>
+          <t>1. Rapid Agent Deployment
+2. Cost-Efficient
+3. Optimized Inferencing
+4. Secure</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Vertical: Health &amp; Life Sciences
-Open Software Platform: OpenVINO Tool Kit
-Intel Technologies: Intel® Xeon® 6 Processors
-Geo Availability: Worldwide</t>
+          <t>Verticals: Healthcare and Life Sciences, Education
+Intel Technologies and Platforms: Intel® Xeon® 6 processors
+Geographical Availability: Worldwide; US/Canada; Latin America Region; Europe, Middle East, and Africa; Asia Pacific, Japan, Australia &amp; New Zealand; PRC; India</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vertical: Health &amp; Life Sciences
-Open Software Platform: OpenVINO Tool Kit
-Intel Technologies: Intel® Xeon® 6 Processors
-Geo Availability: Worldwide</t>
+          <t>Verticals: Healthcare and Life Sciences, Education
+Intel Technologies and Platforms: Intel® Xeon® 6 processors
+Geographical Availability: Worldwide; US/Canada; Latin America Region; Europe, Middle East, and Africa; Asia Pacific, Japan, Australia &amp; New Zealand; PRC; India</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>https://www.arcee.ai/book-a-demo</t>
+          <t>https://on-demand.io/</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>https://www.arcee.ai/</t>
+          <t>https://on-demand.io/; https://www.linkedin.com/company/on-demandio/; https://drive.google.com/drive/folders/1uV8a5ml5G6Q4azmEXBmdDAyGPdC5Yr3h</t>
         </is>
       </c>
       <c r="S2" t="b">
@@ -622,21 +620,21 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25122</v>
+        <v>25183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Circulus</t>
+          <t>SymptomTrace</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Circulus</t>
+          <t>SymptomTrace</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ARCos</t>
+          <t>5G Patient Digital Twin</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -646,63 +644,65 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ARCos</t>
+          <t>5G Patient Digital Twin</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ARCos</t>
+          <t>5G Patient Digital Twin</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Real-Time Edge AI OS for Smart Robotics Control Speed</t>
+          <t>AI Analytics at the Patient Edge</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>ARCos is an advanced robotics cognition operating system designed to enable real-time, autonomous decision-making for industrial robots in manufacturing environments. By
-integrating multimodal AI — including vision, audio, and language — ARCos delivers situational awareness, voice-driven task execution, and adaptive robotic actions directly on-device. Built on Intel® Core™ Ultra Series 3 Processors and Intel® Arc™ graphics, the solution leverages CPU, GPU, and NPU resources to efficiently run vision-language-action models and real-time analytics at the edge. Combined with the OpenVINO™ toolkit, ARCos ensures optimized AI inference, low latency, and scalable deployment without reliance on cloud connectivity. This enables secure, resilient operations, reduces downtime through automated failover, and accelerates robot training and task orchestration—driving smarter, more efficient manufacturing workflows.</t>
+          <t>SymptomTrace’s 5G Patient Digital Twin solution transforms chronic disease management by enabling continuous, personalized care at the patient edge. Using non-invasive sensors and real-time analytics, it captures vital signs, mobility patterns, and behavioral data to create a dynamic digital twin for each patient. Unlike traditional episodic care, the solution enables proactive intervention by detecting risks such as falls or disease progression early, improving outcomes and reducing healthcare costs. Built on Intel® Core™ Ultra and Intel® Xeon® processors with integrated CPU, GPU, and NPU acceleration, and optimized with the OpenVINO™ toolkit and Deep Learning Streamer (DL Streamer), the platform delivers efficient edge inference, secure data processing, and scalable AI
+model deployment. With Intel® Software Guard Extensions (Intel® SGX) for secure enclaves and media acceleration for efficient data handling, healthcare providers gain real-time insights, privacy-first monitoring, and the ability to scale personalized care from hospital to home environments.</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1. Heterogeneous Edge AI
-2. Physical AI
-3. Autonomous Robotics
-4. Deterministic Control</t>
+          <t>1. Secure Edge Data Protection
+2. Efficient Data Management
+3. Scalable AI Model Training
+4. Reliable Home Deployment</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Device Type: Edge Device
-Vertical: Manufacturing; Robotics
-Use Cases: Quality Control; Worker Safety; Anomaly Detection; Quality Inspection; Worker Safety ; Vision Guided Robots ; Autonomous Mobile Robots; Humanoid Robots; VLA Models
-Open Software Platform: Robotics AI Suite; Manufacturing AI Suite; OpenVINO™ Toolkit; oneAPI; Deep Learning Streamer; Intel® Deep Learning Boost
-Intel Technologies: Intel® Core™ Ultra Series 3 processors
-Geo Availability: Worldwide</t>
+          <t>Device Type: Edge Device, Edge Server
+Verticals: Healthcare and Life Sciences
+Vertical Use Cases: Image Analysis, Virtual Care
+Intel Open Software Platform: Health &amp; life Science AI Suite, OpenVINO™ Toolkit, Intel Deep Learning Streamer
+Intel Technologies and Platforms: Intel® Core™ Ultra Series 3 processors, Intel® Core™ Ultra processors (Series 1), 5th Gen Intel® Xeon® Scalable processors, Intel® Xeon® 6 processors, Intel® Arc™ B-Series Graphics
+Geographical Availability: Asia Pacific, Japan, Australia &amp; New Zealand
+Target Audience: Enterprise, SMB (Small or Mid-Sized Business)</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Device Type: Edge Device
-Vertical: Manufacturing; Robotics
-Use Cases: Quality Control; Worker Safety; Anomaly Detection; Quality Inspection; Worker Safety ; Vision Guided Robots ; Autonomous Mobile Robots; Humanoid Robots; VLA Models
-Open Software Platform: Robotics AI Suite; Manufacturing AI Suite; OpenVINO™ Toolkit; oneAPI; Deep Learning Streamer; Intel® Deep Learning Boost
-Intel Technologies: Intel® Core™ Ultra Series 3 processors
-Geo Availability: Worldwide</t>
+          <t>Device Type: Edge Device, Edge Server
+Verticals: Healthcare and Life Sciences
+Vertical Use Cases: Image Analysis, Virtual Care
+Intel Open Software Platform: Health &amp; life Science AI Suite, OpenVINO™ Toolkit, Intel Deep Learning Streamer
+Intel Technologies and Platforms: Intel® Core™ Ultra Series 3 processors, Intel® Core™ Ultra processors (Series 1), 5th Gen Intel® Xeon® Scalable processors, Intel® Xeon® 6 processors, Intel® Arc™ B-Series Graphics
+Geographical Availability: Asia Pacific, Japan, Australia &amp; New Zealand
+Target Audience: Enterprise, SMB (Small or Mid-Sized Business)</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>mailto:info@circul.us; https://circul.us/</t>
+          <t>mailto:service@symptomtrace.com; https://symptomtrace.com/</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>https://circul.us/; http://arcos.circul.us/</t>
+          <t>https://symptomtrace.com/</t>
         </is>
       </c>
       <c r="S3" t="b">
@@ -720,86 +720,86 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25123</v>
+        <v>25173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Circulus</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Circulus</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CanversON</t>
+          <t>SDC Mini PC X29 Ultra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>system</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CanversON</t>
+          <t>SDC Mini PC X29 Ultra</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CanversON</t>
+          <t>SDC Mini PC X29 Ultra</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>On-Device AI Workstations Enable Secure Generative AI</t>
+          <t>Compact AI-Ready Mini PC for High-Performance Computing</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>CanversON transforms Intel® Core™ Ultra-powered AI PCs into fully capable, on-device generative AI workstations for education and enterprise environments. By integrating multimodal AI—including text, image, voice, and digital human generation—the solution eliminates reliance on fragmented cloud services and recurring subscription costs. Leveraging CPU, GPU, and NPU acceleration with the OpenVINO™ toolkit, CanversON delivers optimized, low-latency AI performance directly on the device. This ensures complete data privacy, keeping sensitive information local while enabling offline operation in secure or connectivity-limited settings. With pre-configured educational applications and intuitive interfaces, users can rapidly deploy immersive learning experiences and intelligent workflows. CanversON democratizes access to advanced AI, empowering organizations to scale innovation efficiently, securely, and cost-effectively across diverse environments.</t>
+          <t>SDC Mini PC X29 Ultra delivers high performance and intelligent processing in a compact form factor, designed for enterprise applications and AI-driven workloads. Powered by the Intel® Core™ Ultra X7 processor 358H, it provides advanced processing capabilities for demanding corporate and data intensive environments. With support for artificial intelligence workloads and data analytics through the Intel® Arc™ B390 GPU, the system is optimized for modern AI applications. High-speed connectivity ports enable seamless integration and enhanced productivity across systems and devices. Its compact design supports up to four monitors (1x DP, 1x HDMI, and 2x Type-C) and offers operating system flexibility with Windows 11 Pro or Linux, making it a versatile solution for performance-focused computing environments.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1. Agentic AI-PC
-2. Private AI
-3. Multimodal AI
-4. Secure AI</t>
+          <t>1. High Performance
+2. Compact Form Factor
+3. Supports Up to 4 Monitors
+4. Advanced Connectivity</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Device Type: Edge Device
-Vertical: Education
-Use Cases: Digital Campus ; Intelligent Learning ; Immersive Learning
-Open Software Platform: OpenVINO Tool Kit, oneAPI, Intel® Deep Learning Boost; Education AI Suite
-Intel Technologies: Intel® Core™ Ultra processors (Series 1); Intel® Core™ Ultra processors (Series 2)
-Geo Availability: Worldwide; US/Canada; Latin America Region; Europe, Middle East, and Africa; Asia Pacific, Japan, Australia &amp; New Zealand; PRC; India</t>
+          <t>Edge Features: Real-time
+Verticals: Video Safety &amp; Critical Infrastructure
+Intel Open Software Platform: Education AI Suite, Health &amp; Life Science AI Suite, Manufacturing AI Suite, Robotics AI Suite, OpenVINO™ Toolkit
+Intel Technologies and Platforms: Intel® Core™ Ultra Series 3 processors, Intel® Arc™ Pro B-Series Graphics
+Geographical Availability: Latin America Region
+AI Edge System Sizing: Efficiency Optimized</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Device Type: Edge Device
-Vertical: Education
-Use Cases: Digital Campus ; Intelligent Learning ; Immersive Learning
-Open Software Platform: OpenVINO Tool Kit, oneAPI, Intel® Deep Learning Boost; Education AI Suite
-Intel Technologies: Intel® Core™ Ultra processors (Series 1); Intel® Core™ Ultra processors (Series 2)
-Geo Availability: Worldwide; US/Canada; Latin America Region; Europe, Middle East, and Africa; Asia Pacific, Japan, Australia &amp; New Zealand; PRC; India</t>
+          <t>Edge Features: Real-time
+Verticals: Video Safety &amp; Critical Infrastructure
+Intel Open Software Platform: Education AI Suite, Health &amp; Life Science AI Suite, Manufacturing AI Suite, Robotics AI Suite, OpenVINO™ Toolkit
+Intel Technologies and Platforms: Intel® Core™ Ultra Series 3 processors, Intel® Arc™ Pro B-Series Graphics
+Geographical Availability: Latin America Region
+AI Edge System Sizing: Efficiency Optimized</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>mailto:info@circul.us; https://circul.us/</t>
+          <t>https://sdc.com.br/entre-em-contato/</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>https://circul.us/</t>
+          <t>https://sdc.com.br/produto/minipc-x29-ultra/</t>
         </is>
       </c>
       <c r="S4" t="b">
@@ -817,81 +817,86 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25103</v>
+        <v>25172</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Dynamo AI</t>
+          <t>Advantech</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dynamo AI</t>
+          <t>Advantech</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DynamoGuard On-Device</t>
+          <t>Advantech VEGA-7030</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>system</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DynamoGuard On-Device</t>
+          <t>Advantech VEGA-7030</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>DynamoGuard On-Device</t>
+          <t>Advantech VEGA-7030</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Secure, Real-time AI Guardrails at the Device Level</t>
+          <t>1U High Density Media Server for Accelerated Video Processing</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>DynamoGuard On-Device, powered by Intel® Core™ Ultra processors, delivers real-time on-device guardrails that help enterprises adopt generative AI securely and responsibly. Many organizations lack the oversight, compliance, and data protection needed for safe AI adoption. This solution enables IT teams to rapidly create, customize, and enforce policies that filter AI interactions before transmission—ensuring sensitive inputs never leave the device. With ultra-low latency (&lt;40ms GPU, &lt;135ms NPU) and lightweight guardrail models optimized using the OpenVINO™ toolkit, DynamoGuard minimizes performance overhead while maximizing security. Enterprises gain a single observability platform for monitoring AI usage, real-time compliance enforcement, and hallucination checks. The result is a powerful combination of speed, control, and protection, enabling confident, large-scale deployment of GenAI across enterprise fleets.</t>
+          <t>The VEGA-7030 is a highly configurable, 1U, short-depth video applications server based on the Intel® Core™ desktop processor family. Supporting up to 24 CPU cores with on-board Intel® UHD Graphics and Intel® Quick Sync Video functionality, the VEGA-7030 offers plenty of processing power for many software video workflows while its class-leading four PCI Express slots provide high flexibility to fit a wide range of video accelerators or video I/O cards such as the Advantech VEGA UHD encoding/acquisition cards. VEGA-7030 is ready for integration into streaming networks with three 2.5Gigabit and one Gigabit Ethernet connections and can support latest generation protocols like SRT. It has the look and feel of an appliance with user-programmable front panel LCD and keypad and a small OLED confidence monitor for video display, but inside this is a reliable server architecture with dual redundant 550W power, dual NVMe storages, and options for BMC-based remote management and secure TPM feature.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1. Real-Time Guardrails
-2. On-Device Compliance
-3. Ultra-Low Latency</t>
+          <t>1. Four PCIe Slots for I/O &amp; Accelerators
+2. Four GbE Network Ports
+3. Front Panel LCD Display, Keypad, and Confidence Monitor
+4. Redundant Power Supplies</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Device Type: Edge Device
-Open Software Platform: OpenVINO Tool Kit
-Intel Technologies: Intel® Core™ Ultra processors (Series 1)
-Geo Availability: Worldwide</t>
+          <t>Edge Features: Real-time
+Verticals: Video Safety &amp; Critical Infrastructure
+Intel Open Software Platform: Metro AI Suite, oneAPI
+Intel Technologies and Platforms: Intel® Core™ processors (Series 1), Intel® Core™ processors (Series 2), 13th Gen Intel® Core™ processors, 14th Gen Intel® Core™ processors, Intel® Arc™ B-Series Graphics, Intel® Iris® Xe Graphics
+Geographical Availability: US/Canada; Asia Pacific, Japan, Australia &amp; New Zealand
+AI Edge System Sizing: Mainstream &amp; Entry</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Device Type: Edge Device
-Open Software Platform: OpenVINO Tool Kit
-Intel Technologies: Intel® Core™ Ultra processors (Series 1)
-Geo Availability: Worldwide</t>
+          <t>Edge Features: Real-time
+Verticals: Video Safety &amp; Critical Infrastructure
+Intel Open Software Platform: Metro AI Suite, oneAPI
+Intel Technologies and Platforms: Intel® Core™ processors (Series 1), Intel® Core™ processors (Series 2), 13th Gen Intel® Core™ processors, 14th Gen Intel® Core™ processors, Intel® Arc™ B-Series Graphics, Intel® Iris® Xe Graphics
+Geographical Availability: US/Canada; Asia Pacific, Japan, Australia &amp; New Zealand
+AI Edge System Sizing: Mainstream &amp; Entry</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>mailto:patrick@dynamofl.com; https://www.dynamo.ai/</t>
+          <t>https://www.advantech.com/en/contact</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>https://www.dynamo.ai/</t>
+          <t>https://www.advantech.com/zh-tw/products/2dc1acc7-591f-4c62-a9a3-25a90939ab8a/vega-7030/mod_03cc1600-7ce2-4341-94f6-49c0db1c7754</t>
         </is>
       </c>
       <c r="S5" t="b">
@@ -909,21 +914,21 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25101</v>
+        <v>25170</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ecrio</t>
+          <t>Unstructured</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ecrio</t>
+          <t>Unstructured</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ecrio Edge AI Communication Platform</t>
+          <t>Unstructured</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -933,61 +938,58 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Ecrio Edge AI Communication Platform</t>
+          <t>Unstructured</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Ecrio Edge AI Communication Platform</t>
+          <t>Unstructured</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Low Latency Edge AI for PPE Detection &amp; Multi-Modal Alerting</t>
+          <t>Parse and Enrich Unstructured Data for AI Integration</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Ecrio’s Edge AI Communication Platform enables AI-powered worker safety and mission-critical communications for Human-Oversight of automation by combining real-time video analytics and voice processing at the edge. The solution supports use cases such as Personal Protective Equipment (PPE) detection and voice-driven workflows by processing vision and voice data
-locally, close to where it is generated. Running on containerized workloads, the solution is optimized with OpenVINO™ toolkit, accelerating vision and speech inference on AI PCs powered by Intel® Core™ Ultra 200V series processors. The edge-focused architecture delivers low-latency, real-time decision-making while reducing reliance on centralized cloud infrastructure. Designed for safety-critical operations, the platform delivers resilient, always-on performance even in bandwidth-limited or disconnected environments. Local AI processing enhances data privacy, supports regulatory compliance, and enables consistent, scalable deployment across distributed worksites.</t>
+          <t>Unstructured delivers a robust data preprocessing platform that converts unstructured data—such as PDFs, images, and emails—into structured, AI-ready formats like JSON. Leveraging advanced Optical Character Recognition (OCR) models, including PaddlePaddle and Tesseract, and vision-language model (VLM) pipelines, the platform automates data extraction, parsing, and enrichment. This enables businesses to efficiently prepare large volumes of complex data for downstream AI analytics, search, and chatbot applications. Unstructured is available as an open-source Python library, a cloud-based SaaS API, and a no-code enterprise platform, all of which integrate seamlessly with cloud storage and AI tools to provide flexible, code-free data preparation for modern enterprise workflows.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1. Real-Time Edge AI
-2. On-Device Vision
-3. Low-Latency Voice
-4. Cost-Efficient</t>
+          <t>1. Faster Data Parsing
+2. Optimized OCR Ops
+3. AI-Ready Pipelines
+4. Scalable On-Prem AI</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Vertical: Video Safety &amp; Critical Infrastructure, Manufacturing
-Use Cases: Worker Safety ; Operational Diagnostics; Operational Efficiency
-Open Software Platform: OpenVINO Tool Kit
-Intel Technologies: Intel® Core™ Ultra processors (Series 2)
-Geo Availability: Worldwide</t>
+          <t>Verticals: Horizontal, Video Safety &amp; Critical Infrastructure, Transportation, Manufacturing, Retail, Healthcare and Life Sciences, Education
+Intel Open Software Platform: OpenVINO™ Toolkit
+Intel Technologies and Platforms: Intel® Xeon® 6 processors
+Geographical Availability: Worldwide; US/Canada; Latin America Region; Europe, Middle East, and Africa; Asia Pacific, Japan, Australia &amp; New Zealand; PRC; India</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vertical: Video Safety &amp; Critical Infrastructure, Manufacturing
-Use Cases: Worker Safety ; Operational Diagnostics; Operational Efficiency
-Open Software Platform: OpenVINO Tool Kit
-Intel Technologies: Intel® Core™ Ultra processors (Series 2)
-Geo Availability: Worldwide</t>
+          <t>Verticals: Horizontal, Video Safety &amp; Critical Infrastructure, Transportation, Manufacturing, Retail, Healthcare and Life Sciences, Education
+Intel Open Software Platform: OpenVINO™ Toolkit
+Intel Technologies and Platforms: Intel® Xeon® 6 processors
+Geographical Availability: Worldwide; US/Canada; Latin America Region; Europe, Middle East, and Africa; Asia Pacific, Japan, Australia &amp; New Zealand; PRC; India</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>https://www.ecrio.com/contact/</t>
+          <t>https://unstructured.io/?modal=contact-sales</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>https://www.ecrio.com/</t>
+          <t>https://unstructured.io/</t>
         </is>
       </c>
       <c r="S6" t="b">
@@ -1005,21 +1007,21 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25104</v>
+        <v>25169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EdgeRunner AI</t>
+          <t>Veritone</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EdgeRunner AI</t>
+          <t>Veritone</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>EdgeRunner ODIN</t>
+          <t>VeritoneTrack</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1029,64 +1031,62 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>EdgeRunner ODIN</t>
+          <t>VeritoneTrack</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>EdgeRunner ODIN</t>
+          <t>VeritoneTrack</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>AI Solution for the DoD that Works On-Device</t>
+          <t>AI-Driven Video Analysis for Investigative Workflows</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>EdgeRunner ODIN is an on-device AI solution providing personalized assistance to warfighters. Running entirely on AI PCs, it leverages generative AI and specialized large language models (LLMs) to deliver customized, role-specific support directly on the device.
-Key features include:
-▪ Personalization: Customized AI adapters tailored to individual Military Occupational Specialties (MOS).
-▪ Agentic Capabilities: AI agents that streamline workflows by taking actions and completing tasks.
-▪ Operational Security: Enhanced data protection by eliminating external data transmission.
-Optimized for Intel® Core Ultra processors using the Intel® Distribution of OpenVINO™ toolkit, EdgeRunner ODIN ensures high performance and reliability in denied, degraded, intermittent, and limited bandwidth (DDIL) environments. It accelerates logistics planning, maintenance, and operations reporting while maintaining data security.</t>
+          <t>Veritone Track is an AI-powered video analytics solution that enables investigative teams to efficiently analyze and correlate large volumes of recorded video from multiple sources. The platform connects
+visual evidence across files, cameras, and locations to help surface relevant vehicles, appearances, and activities to reconstruct events across time and place. By generating investigative timelines that reveal movements, interactions, and contextual relationships, Veritone Track helps accelerate missing-person recovery, victim protection, vehicle-based
+investigations, and digital evidence review, transforming fragmented video into actionable investigative insights.</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1. On-Device
-2. Private and Secure
-3. No Internet Needed</t>
+          <t>1. Scalable Video AI
+2. Accelerated Inference
+3. Multi-Stream Analysis
+4. High Throughput Analytics</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Device Type: Edge Device, Edge Server, Data Center,
-Vertical: Video Safety &amp; Critical Infrastructure
-Open Software Platform: OpenVINO Tool Kit
-Intel Technologies: Intel® Core™ Ultra processors (Series 2)
-Geo Availability: Worldwide</t>
+          <t>Device Type: Data Center
+Verticals: Video Safety &amp; Critical Infrastructure
+Intel Open Software Platform: OpenVINO™ Toolkit
+Intel Technologies and Platforms: Intel® Xeon® 6 processors
+Geographical Availability: Worldwide; US/Canada; Latin America Region; Europe, Middle East, and Africa; Asia Pacific, Japan, Australia &amp; New Zealand; PRC; India</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Device Type: Edge Device, Edge Server, Data Center,
-Vertical: Video Safety &amp; Critical Infrastructure
-Open Software Platform: OpenVINO Tool Kit
-Intel Technologies: Intel® Core™ Ultra processors (Series 2)
-Geo Availability: Worldwide</t>
+          <t>Device Type: Data Center
+Verticals: Video Safety &amp; Critical Infrastructure
+Intel Open Software Platform: OpenVINO™ Toolkit
+Intel Technologies and Platforms: Intel® Xeon® 6 processors
+Geographical Availability: Worldwide; US/Canada; Latin America Region; Europe, Middle East, and Africa; Asia Pacific, Japan, Australia &amp; New Zealand; PRC; India</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>https://www.edgerunnerai.com/contact</t>
+          <t>https://unlock.veritone.com/corp-contact-us</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>https://www.edgerunnerai.com/; https://www.intel.com/content/www/us/en/content-details/862002/enhancing-defense-capabilities-with-edge-runner-ai.html; https://www.youtube.com/watch?v=jHBriPavdZI</t>
+          <t>https://www.veritone.com/</t>
         </is>
       </c>
       <c r="S7" t="b">
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25116</v>
+        <v>25168</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Examroom.AI</t>
+          <t>JAAN Innovations</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Examroom.AI</t>
+          <t>JAAN Innovations</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Examroom.AI Sentence Predictor</t>
+          <t>HawkEye2.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1128,62 +1128,65 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Examroom.AI Sentence Predictor</t>
+          <t>HawkEye</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Examroom.AI Sentence Predictor</t>
+          <t>HawkEye2.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>AI-Driven Sentence Prediction for High-Velocity Writing</t>
+          <t>Smarter Parking Automation Powered by Intel® AI Technologies</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Examroom.AI's Sentence Predictor is an AI-powered writing assistant that boosts productivity by generating the next sentence or phrase in real time as users type. Leveraging
-advanced language-model intelligence, Sentence Predictor delivers smart autocomplete that accelerates content creation, improves clarity with context-aware suggestions, and helps users strengthen
-sentence structure, tone, and vocabulary, and multilingual writing support. Sentence Predictor supports professionals and students across documents, chat interfaces and search experiences -- enabling more natural chatbot responses and more precise, predictive query completion across multiple languages. Powered by Intel® Xeon® Platinum 8568Y+ processors paired with Intel® Gaudi® 3 AI accelerators, Sentence Predictor benefits from faster large-model training, efficient scaling, and reduced fine-tuning, resulting in highly responsive, cost-efficient predictive writing experiences.</t>
+          <t>HawkEye2.0 by JAAN Innovations is an AI-driven, edge-intelligent smart parking platform with real-time vehicle detection, automated access control, and dynamic capacity management in high-traffic environments.
+Built on Intel® Core Ultra processors and optimized with the OpenVINO™ Toolkit, HawkEye 2.0 showcases how Intel’s AI-accelerated CPU architecture enables scalable, multi-stream computer vision workloads—without reliance on discrete GPUs. Leveraging existing IP cameras as intelligent sensors, advanced AI algorithms, and an API-first open platform architecture, HawkEye 2.0 integrates easily with existing infrastructure to:
+▪ Automate entry/exit using AI-powered ANPR
+▪ Track real-time bay occupancy
+▪ Guide drivers to nearest available space
+▪ Actionable insights and centralized dashboard
+With edge-based AI inference, HawkEye2.0 ensures low-latency decision-making—even in bandwidth-constrained or intermittent network environments—while maintaining high performance and reliability at scale.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1. Fast Auto-Complete
-2. Context-Aware Prediction
-3. Scalable Model Inference
-4. Cost-Efficient</t>
+          <t>1. Faster AI Inference
+2. 24 HD Streams / Node
+3. High-Load Stability</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Device Type: Edge Server, Data Center,
-Vertical: Horizontal, Education
-Use Cases: Intelligent Learning
-Intel Technologies: 5ht Gen Intel® Xeon® processors
-Geo Availability: Worldwide</t>
+          <t>Device Type: Edge Server
+Verticals: Horizontal, Video Safety &amp; Critical Infrastructure, Transportation, Retail, Healthcare and Life Sciences
+Intel Open Software Platform: OpenVINO™ Toolkit
+Intel Technologies and Platforms: Intel® Core™ Ultra processors (Series 2)
+Geographical Availability: US/Canada; Europe, Middle East, and Africa; Asia Pacific, Japan, Australia &amp; New Zealand</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Device Type: Edge Server, Data Center,
-Vertical: Horizontal, Education
-Use Cases: Intelligent Learning
-Intel Technologies: 5ht Gen Intel® Xeon® processors
-Geo Availability: Worldwide</t>
+          <t>Device Type: Edge Server
+Verticals: Horizontal, Video Safety &amp; Critical Infrastructure, Transportation, Retail, Healthcare and Life Sciences
+Intel Open Software Platform: OpenVINO™ Toolkit
+Intel Technologies and Platforms: Intel® Core™ Ultra processors (Series 2)
+Geographical Availability: US/Canada; Europe, Middle East, and Africa; Asia Pacific, Japan, Australia &amp; New Zealand</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>https://www.examroom.ai/contact-us</t>
+          <t>mailto:ajay.masur@jaaninnovations.com; https://www.hawkeyeparking.net/contact-us/</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>https://www.examroom.ai/</t>
+          <t>https://www.hawkeyeparking.net/contact-us/</t>
         </is>
       </c>
       <c r="S8" t="b">
@@ -1201,21 +1204,21 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25106</v>
+        <v>25167</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Kamiwaza</t>
+          <t>Aktek</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kamiwaza</t>
+          <t>Aktek</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AI Orchestration</t>
+          <t>Knowledge Base Agents Platform</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1225,823 +1228,65 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>AI Orchestration</t>
+          <t>Knowledge Base Agents Platform</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>AI Orchestration</t>
+          <t>Knowledge Base Agents Platform</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Deploy Purpose-Built AI Agents for Enterprise Workloads</t>
+          <t>Unlock Data-Driven Growth With Advanced Analytics</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Kamiwaza's AI Orchestration Engine accelerates enterprise AI adoption by enabling seamless deployment across cloud, on-prem, and edge environments. Its Inference Mesh and Distributed Data Engine allow data to stay where it resides, transmitting only inference requests and results—reducing latency and preserving privacy. Relationship-Based Access Control (ReBAC) adds contextual intelligence to ensure only authorized users access sensitive data, aligning with enterprise-grade security. With exposed APls, SDKs, and Model Context Protocol (MCP), Kamiwaza integrates easily into existing systems. The App Garden offers deployable AI agents for workloads like document processing and digital compliance, helping teams operationalize AI faster and more securely.</t>
+          <t>Aktek's knowledge-based agents provide enterprises with a secure, intelligent, and efficient way to access and utilize their internal information. Purpose-built for data sensitive environments, these advanced
+digital assistants can retrieve, analyze, and deliver contextually relevant insights from large internal knowledge bases. Operating entirely within an organization's secure infrastructure, they eliminate reliance on external APls while ensuring full data control and compliance. By streamlining information retrieval, improving decision-making, and preserving confidentiality, Aktek empowers organizations to unlock the true value of their internal knowledge and enhance overall operational efficiency.</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1. AI Agents for Enterprise
-2. Inference Mesh
-3. Distributed Data Engine
-4. ReBAC</t>
+          <t>1. Fast Data Processing
+2. Scalable
+3. Real-Time Insights
+4. Secure</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Device Type: Edge Server, Data Center,
-Vertical: Horizontal, Video Safety &amp; Critical Infrastructure, Manufacturing, Health &amp; Life Sciences, Education
-Intel Technologies: Intel® Xeon® 6 Processors
-Geo Availability: Worldwide</t>
+          <t>Verticals: Horizontal, Manufacturing, Retail, Healthcare and Life Sciences, Education
+Intel Open Software Platform: OpenVINO™ Toolkit
+Intel Technologies and Platforms: Intel® Core™ Ultra processors (Series 2)
+Geographical Availability: Europe, Middle East, and Africa; Asia Pacific, Japan, Australia &amp; New Zealand</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Device Type: Edge Server, Data Center,
-Vertical: Horizontal, Video Safety &amp; Critical Infrastructure, Manufacturing, Health &amp; Life Sciences, Education
-Intel Technologies: Intel® Xeon® 6 Processors
-Geo Availability: Worldwide</t>
+          <t>Verticals: Horizontal, Manufacturing, Retail, Healthcare and Life Sciences, Education
+Intel Open Software Platform: OpenVINO™ Toolkit
+Intel Technologies and Platforms: Intel® Core™ Ultra processors (Series 2)
+Geographical Availability: Europe, Middle East, and Africa; Asia Pacific, Japan, Australia &amp; New Zealand</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>https://www.kamiwaza.ai/get-started</t>
+          <t>https://aktekbilisim.com/iletisim-formu/</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>https://www.kamiwaza.ai/</t>
+          <t>https://www.aktekbilisim.com/en/</t>
         </is>
       </c>
       <c r="S9" t="b">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="b">
-        <v>1</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>PS-009</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>25107</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LLMWare.ai</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>LLMWare.ai</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Model HQ - Local AI</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>application</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Model HQ - Local AI</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Model HQ - Local AI</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Securely Deploy and Scale AI Across the Enterprise</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>The Intel + LLMWare.ai solution provides a private, no-code, and affordable AI platform for enterprises to build and deploy AI agents, chatbots, and GenAI applications on AI PCs powered by Intel and servers with Intel® Xeon® processors. It mitigates cloud-related risks and unpredictable costs while supporting secure local inferencing and scalable RAG workflows. With over 100 small language models, Model HQ enables fast, code-free development of AI apps, keeping data private and within the enterprise.</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>1. Local AI Inferencing
-2. RAG (Hybrid AI) Scaling
-3. No-Code Agent Creation
-4. 100+ Small Models</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Device Type: Edge Server, Data Center,
-Vertical: Horizontal, Video Safety &amp; Critical Infrastructure, Transportation, Manufacturing, Retail, Health &amp; Life Sciences, Education
-Intel Technologies: Intel® Xeon® 6 Processors, 5th Gen Intel® Xeon® Processors
-Geo Availability: Worldwide</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Device Type: Edge Server, Data Center,
-Vertical: Horizontal, Video Safety &amp; Critical Infrastructure, Transportation, Manufacturing, Retail, Health &amp; Life Sciences, Education
-Intel Technologies: Intel® Xeon® 6 Processors, 5th Gen Intel® Xeon® Processors
-Geo Availability: Worldwide</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>https://llmware.ai/contact-us</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>https://llmware.ai/intel</t>
-        </is>
-      </c>
-      <c r="S10" t="b">
-        <v>0</v>
-      </c>
-      <c r="T10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="b">
-        <v>1</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>PS-010</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>25108</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>MVision</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MVision</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Contour+</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>application</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Contour+</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Contour+</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Contour+: Guideline-Based Auto-Contouring for Radiotherapy</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Contour+ by MVision revolutionizes radiotherapy with AI-driven automation. It streamlines contouring, creating more precise, guideline-compliant organ and target delineations in minutes. By reducing manual effort, it saves clinicians valuable time, boosting efficiency and consistency across radiotherapy treatment plans. Its advanced algorithms ensure high quality of
-contours, minimizing errors and enhancing treatment. Contour+ integrates seamlessly into workflows, supporting diverse imaging modalities. Trusted globally, it empowers oncology teams to deliver faster and improved patient care.</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>1. Faster Decision-Making
-2. Multiple Modalities
-3. High Quality Images
-4. Reduced Latency</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Vertical: Health &amp; Life Sciences
-Geo Availability: Worldwide</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Vertical: Health &amp; Life Sciences
-Geo Availability: Worldwide</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>https://mvision.ai/</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>https://mvision.ai/contour/</t>
-        </is>
-      </c>
-      <c r="S11" t="b">
-        <v>0</v>
-      </c>
-      <c r="T11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="b">
-        <v>1</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>PS-011</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>25109</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Niotek</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Niotek</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>HORUS</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>application</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>HORUS</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>HORUS</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Quality Control, Efficiency, and Operational Excellence</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Niotek's HORUS, powered by Intel® Core™ Ultra processors and the OpenVINO™ toolkit, is an industrial digital twin platform with advanced process visibility, predictive analytics, and AI-driven optimization. Built for scalability and seamless integration, HORUS connects with existing production environments, providing instant value without complex overhauls. By leveraging industrial loT, augmented reality, and AI, HORUS enables smarter decision-making, proactive maintenance, reducing downtime—all while providing robust on-premise data privacy and control.</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>1. Image Classification
-2. Hybrid Architecture Support
-3. Cost-Efficient
-4. Enhanced Data Privacy</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Vertical: Manufacturing
-Use Cases: Quality Control; Quality Inspection; Operational Diagnostics
-Open Software Platform: OpenVINO Tool Kit
-Intel Technologies: Intel® Core™ Ultra processors (Series 2); Intel® Core™ Ultra processors (Series 1)
-Geo Availability: Europe, Middle East, and Africa</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Vertical: Manufacturing
-Use Cases: Quality Control; Quality Inspection; Operational Diagnostics
-Open Software Platform: OpenVINO Tool Kit
-Intel Technologies: Intel® Core™ Ultra processors (Series 2); Intel® Core™ Ultra processors (Series 1)
-Geo Availability: Europe, Middle East, and Africa</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>https://niotek.net/en/contact</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>https://niotek.net/en; https://niotek.net/en/products</t>
-        </is>
-      </c>
-      <c r="S12" t="b">
-        <v>0</v>
-      </c>
-      <c r="T12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="b">
-        <v>1</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>PS-012</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>25110</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Red Hat</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Red Hat</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>OpenShift AI</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>application</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>OpenShift AI</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>OpenShift AI</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Scalable MLOps with Advanced Training, Tuning, and Inferencing</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Red Hat® OpenShift® AI is an enterprisegrade platform designed to streamline the development, deployment and management of AI applications across hybrid cloud environments. By integrating Intel® Gaudi® AI accelerators, OpenShift AI enhances the performance of deep learning workloads, offering efficient model training and inference capabilities. The platform also supports the Open Platform for Enterprise AI (OPEA), providing a flexible framework for building and scaling AI solutions. This combination enables organizations to leverage advanced hardware acceleration and open-source tools to optimize AI workflows, ensuring scalability and efficiency in various deployment scenarios.</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>1. Integrated Data Handling
-2. Scalable Development &amp; Deployment
-3. Model Training &amp; Fine-Tuning
-4. Model Serving &amp; Deployment
-5. Security &amp; Governance</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Vertical: Horizontal, Retail, Health &amp; Life Sciences
-Intel Technologies: Intel® Xeon® 6 Processors
-Geo Availability: Worldwide</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Vertical: Horizontal, Retail, Health &amp; Life Sciences
-Intel Technologies: Intel® Xeon® 6 Processors
-Geo Availability: Worldwide</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>https://www.redhat.com/en/products/ai/openshift-ai#form</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>https://www.redhat.com/en; https://www.redhat.com/en/products/ai/openshift-ai</t>
-        </is>
-      </c>
-      <c r="S13" t="b">
-        <v>0</v>
-      </c>
-      <c r="T13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="b">
-        <v>1</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>PS-013</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>25111</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Tetherfi</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Tetherfi</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Patented Speech-to-Text Solution</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>application</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Patented Speech-to-Text Solution</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Patented Speech-to-Text Solution</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Edge AI Enabled Speech-to-Text for Faster and Secure Customer Engagement</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Tetherfi's AI-powered speech-to-text engine at the Edge transforms voice interactions into accurate, real-time transcripts, enabling enterprises to deliver seamless and secure customer experiences. Designed for industries with high customer engagement such as Banking, Insurance, Financial Services, Utilities, and Telecom, Tetherfi’s Speech AI-powered real-time speech-to-text enhances contact center performance by enabling faster call handling, automated post-call summarization, and real-time insights into customer intent and sentiment—driving better customer experiences using sovereign data. Powered by Intel® Xeon® 6 processors and optimized with OpenVINO™ toolkit, Tetherfi achieves up to 4x speedup for BF16 precision and supports multiple concurrent streams without performance loss, ensuring fast, reliable transcription for mission-critical environments.</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>1. Reduced Latency
-2. Real-Time Transcription
-3. Multi-Stream Support
-4. Scalable AI Performance</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Device Type: Edge Device, Edge Server
-Vertical: Horizontal, Retail, Health &amp; Life Sciences
-Open Software Platform: OpenVINO Tool Kit
-Intel Technologies: Intel® Xeon® 6 Processors
-Geo Availability: Worldwide</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Device Type: Edge Device, Edge Server
-Vertical: Horizontal, Retail, Health &amp; Life Sciences
-Open Software Platform: OpenVINO Tool Kit
-Intel Technologies: Intel® Xeon® 6 Processors
-Geo Availability: Worldwide</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>mailto:sales@tetherfi.com; https://tetherfi.com/</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>https://tetherfi.com/</t>
-        </is>
-      </c>
-      <c r="S14" t="b">
-        <v>0</v>
-      </c>
-      <c r="T14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="b">
-        <v>1</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>PS-014</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>25112</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>VNClagoon</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>VNClagoon</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VNClagoon GenAI Platform</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>application</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>VNClagoon GenAI Platform</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>VNClagoon GenAI Platform</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>High-Speed GenAI Processing — Security by Design</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>VNClagoon is the secure, open-source based collaboration suite that gives regulated organizations full control over sensitive data while unlocking generative AI. Built for the requirements of financial services, healthcare, and public sector, it combines enterprise-grade tools—secure email, team chat, CRM, and real-time dashboards—with a built-in GenAI assistant
-that automates workflows without ever leaving your perimeter. Deploy on-premises or in private data centers. Scale instantly with modular architecture. Stay compliant without sacrificing speed.
-VNClagoon + Intel: Run tomorrow’s AI today—100% on your infrastructure, 100% under your rules.</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>1. Private AI Execution
-2. Secure Data Handling
-3. Fast GenAI Inference
-4. Flexible Deployment</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Device Type: Edge Server
-Vertical: Health &amp; Life Sciences
-Open Software Platform: OpenVINO Tool Kit
-Intel Technologies: Intel® Core™ Ultra processors (Series 1); Intel® Xeon® 6 Processors; 5th Gen Intel® Xeon® Processors
-Geo Availability: Worldwide</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Device Type: Edge Server
-Vertical: Health &amp; Life Sciences
-Open Software Platform: OpenVINO Tool Kit
-Intel Technologies: Intel® Core™ Ultra processors (Series 1); Intel® Xeon® 6 Processors; 5th Gen Intel® Xeon® Processors
-Geo Availability: Worldwide</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>https://calendly.com/vnclagoon</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>https://vnclagoon.com/; https://www.intel.com/content/www/us/en/content-details/845715/intel-and-vnclagoon-high-speed-genai-processing-with-security-by-design.html</t>
-        </is>
-      </c>
-      <c r="S15" t="b">
-        <v>0</v>
-      </c>
-      <c r="T15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="b">
-        <v>1</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>PS-015</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>25113</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Wallaroo.AI</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Wallaroo.AI</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Universal AI Inference Platform</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>application</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Universal AI Inference Platform</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Universal AI Inference Platform</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Turnkey AI Inference on CPU/GPU with Observability &amp; Management</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Wallaroo's turnkey universal AI inference platform accelerates deployment for any AI model on any hardware anywhere in minutes. Automated scaling and load balancing ensure seamless streamlined performance, optimizing latency and maximizing throughput while reducing costs. The centralized control plane provides automated real-time AI inference management for auditing, versioning, and monitoring with intuitive analytics for automated drift detection, tracking model performance issues early and maintaining model accuracy. Supporting inline model upgrades with zero
-downtime maximizes model availability, ensuring AI-driven insights deliver continuous value.</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>1. Rapid Model Deployment
-2. Optimized Inferencing
-3. AI Lifecycle Management</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Device Type: Edge Device, Edge Server, Data Center,
-Vertical: Retail, Health &amp; Life Sciences
-Open Software Platform: OpenVINO Tool Kit
-Geo Availability: Worldwide</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Device Type: Edge Device, Edge Server, Data Center,
-Vertical: Retail, Health &amp; Life Sciences
-Open Software Platform: OpenVINO Tool Kit
-Geo Availability: Worldwide</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>https://wallaroo.ai/request-a-demo/</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>https://wallaroo.ai/</t>
-        </is>
-      </c>
-      <c r="S16" t="b">
-        <v>0</v>
-      </c>
-      <c r="T16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="b">
-        <v>1</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>PS-016</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>25114</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Dell</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Dell</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Dell Pro 5 Micro Desktop</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>system</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Dell Pro 5 Micro Desktop</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Dell Pro 5 Micro Desktop</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Ultracompact Edge AI Power with Intel® Core™ Ultra Series 3 Processors</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>The Dell Pro 5 Micro Desktop delivers powerful edge AI performance in a compact, modular form factor designed for modern business environments. Powered by Intel® Core™ Ultra
-Series 3 processors, it integrates advanced AI acceleration with high-performance computing and graphics to enable real-time analytics, automation, and intelligent decision-making at the edge. Its customizable expansion port offers flexible connectivity—from ultra-high-resolution displays to high-speed I/O and legacy interfaces—supporting diverse deployment scenarios. The system’s compact, serviceable design also incorporates sustainable materials and simplifies upgrades and maintenance in space-constrained settings. By combining efficient performance, built-in AI capabilities,
-and adaptable connectivity, the Dell Pro 5 Micro Desktop helps organizations reduce latency, streamline operations, and scale edge AI deployments efficiently, making it a versatile solution for
-retail, industrial, and enterprise applications.</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>1. Security &amp; Reliability
-2. Power Efficiency
-3. Remote Manageability
-4. Intel vPro® Options</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Edge Feature: Real-time
-Vertical: Horizontal, Video Safety &amp; Critical Infrastructure, Transportation, Manufacturing; Robotics, Retail, Health &amp; Life Sciences, Education
-Open Software Platform: Metro AI Suite, Retail AI Suite, Manufacturing AI Suite, Robotics AI Suite, Health &amp; Life Science AI Suite, Education AI Suite, OpenVINO Tool Kit, oneAPI, Deep Learning Streamer, Geti, Intel Deep Learning Boost, Intel SceneScape
-Intel Processors: Intel Core Ultra Series 3 processors
-Intel Graphics: Intel Arc B-Series Graphics
-Geo Availability: Worldwide; US/Canada; Latin America Region; Europe, Middle East, and Africa; Asia Pacific, Japan, Australia &amp; New Zealand
-AI Edge System Sizing: Efficiency Optimized
-Target Audience: Enterprise, SMB (Small or Mid-Sized Business), SI (System Integrators), VAR (Value-Added Reseller)</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Edge Feature: Real-time
-Vertical: Horizontal, Video Safety &amp; Critical Infrastructure, Transportation, Manufacturing; Robotics, Retail, Health &amp; Life Sciences, Education
-Open Software Platform: Metro AI Suite, Retail AI Suite, Manufacturing AI Suite, Robotics AI Suite, Health &amp; Life Science AI Suite, Education AI Suite, OpenVINO Tool Kit, oneAPI, Deep Learning Streamer, Geti, Intel Deep Learning Boost, Intel SceneScape
-Intel Processors: Intel Core Ultra Series 3 processors
-Intel Graphics: Intel Arc B-Series Graphics
-Geo Availability: Worldwide; US/Canada; Latin America Region; Europe, Middle East, and Africa; Asia Pacific, Japan, Australia &amp; New Zealand
-AI Edge System Sizing: Efficiency Optimized
-Target Audience: Enterprise, SMB (Small or Mid-Sized Business), SI (System Integrators), VAR (Value-Added Reseller)</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>https://www.dell.com/en-us/lp/contact-us</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>https://www.dell.com/en-us/shop/desktop-computers/dell-pro-5-micro-desktop/spd/dell-pro-p5m1260-micro/xcto_p5m1260_usr?redirectTo=SOC</t>
-        </is>
-      </c>
-      <c r="S17" t="b">
-        <v>0</v>
-      </c>
-      <c r="T17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testdata/partner_products.xlsx
+++ b/testdata/partner_products.xlsx
@@ -520,15 +520,17 @@
     </row>
     <row r="2">
       <c r="A2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>PS-001</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>25185</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>25185</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -612,15 +614,17 @@
     </row>
     <row r="3">
       <c r="A3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>PS-002</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>25183</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>25183</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -719,8 +723,10 @@
           <t>PS-003</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>25173</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>25173</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -809,15 +815,17 @@
     </row>
     <row r="5">
       <c r="A5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>PS-004</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>25172</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>25172</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -906,15 +914,17 @@
     </row>
     <row r="6">
       <c r="A6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>PS-005</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>25170</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>25170</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -999,15 +1009,17 @@
     </row>
     <row r="7">
       <c r="A7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>PS-006</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>25169</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>25169</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1096,15 +1108,17 @@
     </row>
     <row r="8">
       <c r="A8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>PS-007</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>25168</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>25168</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1196,15 +1210,17 @@
     </row>
     <row r="9">
       <c r="A9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>PS-008</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>25167</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>25167</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
